--- a/examples/sales_2025.xlsx
+++ b/examples/sales_2025.xlsx
@@ -442,7 +442,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Lumen Supply Co. — Orders 2025</t>
+          <t>Lumen Supply Co. Orders 2025</t>
         </is>
       </c>
     </row>
